--- a/team colors.xlsx
+++ b/team colors.xlsx
@@ -1,20 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\mlb-rivalry-tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43496297-6E6E-4DDC-A5C7-25C02B02B171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0BC2828-D7C3-46E4-9711-D2C6C769D3E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-165" yWindow="-165" windowWidth="29130" windowHeight="17610" xr2:uid="{05935388-EEDF-49E3-8C2E-1888B4FAC3CE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{05935388-EEDF-49E3-8C2E-1888B4FAC3CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$1:$B$34</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t>    'ana': {'id': 108, 'color': '#BA0021', 'name': 'Los Angeles Angels'},</t>
   </si>
@@ -147,6 +151,210 @@
   </si>
   <si>
     <t>loser</t>
+  </si>
+  <si>
+    <t>Team Name</t>
+  </si>
+  <si>
+    <t>Team Code</t>
+  </si>
+  <si>
+    <t>Los Angeles Angels</t>
+  </si>
+  <si>
+    <t>Arizona Diamondbacks</t>
+  </si>
+  <si>
+    <t>Atlanta Braves</t>
+  </si>
+  <si>
+    <t>Baltimore Orioles</t>
+  </si>
+  <si>
+    <t>Boston Red Sox</t>
+  </si>
+  <si>
+    <t>Chicago White Sox</t>
+  </si>
+  <si>
+    <t>Chicago Cubs</t>
+  </si>
+  <si>
+    <t>Cincinnati Reds</t>
+  </si>
+  <si>
+    <t>Cleveland Guardians</t>
+  </si>
+  <si>
+    <t>Colorado Rockies</t>
+  </si>
+  <si>
+    <t>Detroit Tigers</t>
+  </si>
+  <si>
+    <t>Houston Astros</t>
+  </si>
+  <si>
+    <t>Kansas City Royals</t>
+  </si>
+  <si>
+    <t>Los Angeles Dodgers</t>
+  </si>
+  <si>
+    <t>Miami Marlins</t>
+  </si>
+  <si>
+    <t>Milwaukee Brewers</t>
+  </si>
+  <si>
+    <t>Minnesota Twins</t>
+  </si>
+  <si>
+    <t>Montreal Expos</t>
+  </si>
+  <si>
+    <t>New York Yankees</t>
+  </si>
+  <si>
+    <t>New York Mets</t>
+  </si>
+  <si>
+    <t>Oakland Athletics</t>
+  </si>
+  <si>
+    <t>Philadelphia Phillies</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates</t>
+  </si>
+  <si>
+    <t>San Diego Padres</t>
+  </si>
+  <si>
+    <t>Seattle Mariners</t>
+  </si>
+  <si>
+    <t>San Francisco Giants</t>
+  </si>
+  <si>
+    <t>St. Louis Cardinals</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rays</t>
+  </si>
+  <si>
+    <t>Texas Rangers</t>
+  </si>
+  <si>
+    <t>Toronto Blue Jays</t>
+  </si>
+  <si>
+    <t>Washington Nationals</t>
+  </si>
+  <si>
+    <t>AL All-Stars</t>
+  </si>
+  <si>
+    <t>NL All-Stars</t>
+  </si>
+  <si>
+    <t>ana</t>
+  </si>
+  <si>
+    <t>ari</t>
+  </si>
+  <si>
+    <t>atl</t>
+  </si>
+  <si>
+    <t>bal</t>
+  </si>
+  <si>
+    <t>bos</t>
+  </si>
+  <si>
+    <t>cha</t>
+  </si>
+  <si>
+    <t>chn</t>
+  </si>
+  <si>
+    <t>cin</t>
+  </si>
+  <si>
+    <t>cle</t>
+  </si>
+  <si>
+    <t>col</t>
+  </si>
+  <si>
+    <t>det</t>
+  </si>
+  <si>
+    <t>hou</t>
+  </si>
+  <si>
+    <t>kca</t>
+  </si>
+  <si>
+    <t>lan</t>
+  </si>
+  <si>
+    <t>mia</t>
+  </si>
+  <si>
+    <t>mil</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>mon</t>
+  </si>
+  <si>
+    <t>nya</t>
+  </si>
+  <si>
+    <t>nyn</t>
+  </si>
+  <si>
+    <t>oak</t>
+  </si>
+  <si>
+    <t>phi</t>
+  </si>
+  <si>
+    <t>pit</t>
+  </si>
+  <si>
+    <t>sdn</t>
+  </si>
+  <si>
+    <t>sea</t>
+  </si>
+  <si>
+    <t>sfn</t>
+  </si>
+  <si>
+    <t>sln</t>
+  </si>
+  <si>
+    <t>tba</t>
+  </si>
+  <si>
+    <t>tex</t>
+  </si>
+  <si>
+    <t>tor</t>
+  </si>
+  <si>
+    <t>was</t>
+  </si>
+  <si>
+    <t>alas</t>
+  </si>
+  <si>
+    <t>nlas</t>
   </si>
 </sst>
 </file>
@@ -218,7 +426,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -226,6 +434,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -570,109 +779,109 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{191F965B-479F-465D-98C1-E0D98B7B46DE}">
   <dimension ref="B2:G34"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="59.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="59.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>18</v>
       </c>
       <c r="C20" s="2"/>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>19</v>
       </c>
@@ -685,13 +894,13 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>20</v>
       </c>
       <c r="C22" s="4"/>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>21</v>
       </c>
@@ -703,57 +912,57 @@
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>32</v>
       </c>
@@ -761,4 +970,295 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7C95E96-19C6-4A3C-B347-BAB0FF1D8099}">
+  <dimension ref="A1:B34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B34" xr:uid="{B7C95E96-19C6-4A3C-B347-BAB0FF1D8099}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B34">
+      <sortCondition ref="A1:A34"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>